--- a/research/traditional_assets/database/data/mexico/mexico_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.09525</v>
+        <v>0.0852</v>
       </c>
       <c r="E2">
-        <v>0.136</v>
+        <v>0.1053</v>
       </c>
       <c r="F2">
-        <v>0.134</v>
+        <v>0.11675</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.004391812583274279</v>
+        <v>0.001989310685289199</v>
       </c>
       <c r="J2">
-        <v>0.00336828034304569</v>
+        <v>0.00167681616552411</v>
       </c>
       <c r="K2">
-        <v>4174.2</v>
+        <v>4525.8</v>
       </c>
       <c r="L2">
-        <v>0.3216514864302557</v>
+        <v>0.2895548361505291</v>
       </c>
       <c r="M2">
-        <v>1000.888</v>
+        <v>3080.01</v>
       </c>
       <c r="N2">
-        <v>0.01877395541540102</v>
+        <v>0.05587644089997061</v>
       </c>
       <c r="O2">
-        <v>0.2397795984859374</v>
+        <v>0.6805448760440144</v>
       </c>
       <c r="P2">
-        <v>758.5</v>
+        <v>2525.8</v>
       </c>
       <c r="Q2">
-        <v>0.01422741124139931</v>
+        <v>0.04582216110504374</v>
       </c>
       <c r="R2">
-        <v>0.1817114656700685</v>
+        <v>0.5580891776039595</v>
       </c>
       <c r="S2">
-        <v>242.388</v>
+        <v>554.21</v>
       </c>
       <c r="T2">
-        <v>0.242172950420027</v>
+        <v>0.1799377274749108</v>
       </c>
       <c r="U2">
-        <v>10725.7</v>
+        <v>11212.8</v>
       </c>
       <c r="V2">
-        <v>0.2011851611758426</v>
+        <v>0.2034186111484022</v>
       </c>
       <c r="W2">
-        <v>0.128349045826806</v>
+        <v>0.1573631179415821</v>
       </c>
       <c r="X2">
-        <v>0.07574794275743615</v>
+        <v>0.111442379742262</v>
       </c>
       <c r="Y2">
-        <v>0.0526011030693698</v>
+        <v>0.04592073819932005</v>
       </c>
       <c r="Z2">
-        <v>0.1316343908775102</v>
+        <v>0.1571173552032647</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04875004297639418</v>
+        <v>0.07873173132854988</v>
       </c>
       <c r="AC2">
-        <v>-0.04934876250492594</v>
+        <v>-0.07873173132854988</v>
       </c>
       <c r="AD2">
-        <v>76408.3</v>
+        <v>95847.59999999999</v>
       </c>
       <c r="AE2">
-        <v>511.3284569090819</v>
+        <v>324.5333806339638</v>
       </c>
       <c r="AF2">
-        <v>76919.62845690908</v>
+        <v>96172.13338063395</v>
       </c>
       <c r="AG2">
-        <v>66193.92845690908</v>
+        <v>84959.33338063395</v>
       </c>
       <c r="AH2">
-        <v>0.5906344472562642</v>
+        <v>0.6356641752361517</v>
       </c>
       <c r="AI2">
-        <v>0.688020043900278</v>
+        <v>0.7291864486656114</v>
       </c>
       <c r="AJ2">
-        <v>0.5538939201857519</v>
+        <v>0.6065008993736445</v>
       </c>
       <c r="AK2">
-        <v>0.6549131895040406</v>
+        <v>0.7040235561423681</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>479.770815019465</v>
+        <v>998.4124999999999</v>
       </c>
       <c r="AP2">
-        <v>415.6343617789092</v>
+        <v>884.9930560482703</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Grupo Financiero Inbursa, S.A.B. de C.V. (BMV:GFINBUR O)</t>
+          <t>Banco Santander México, S.A., Institución de Banca Múltiple, Grupo Financiero Santander México (BMV:BSMX B)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,13 +719,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.171</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="E3">
-        <v>0.127</v>
+        <v>0.0746</v>
       </c>
       <c r="F3">
-        <v>0.135</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,97 +734,103 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.008062157770427372</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>0.006273594048057571</v>
       </c>
       <c r="K3">
-        <v>831.7</v>
+        <v>1266.6</v>
       </c>
       <c r="L3">
-        <v>0.5609361300330479</v>
+        <v>0.3284154847408406</v>
       </c>
       <c r="M3">
-        <v>179.1</v>
+        <v>982.9</v>
       </c>
       <c r="N3">
-        <v>0.02389114920296138</v>
+        <v>0.1219357880111155</v>
       </c>
       <c r="O3">
-        <v>0.2153420704580979</v>
+        <v>0.7760145270803727</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>982.9</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.1219357880111155</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.7760145270803727</v>
       </c>
       <c r="S3">
-        <v>179.1</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>853.8</v>
+        <v>3839.1</v>
       </c>
       <c r="V3">
-        <v>0.1138931501367305</v>
+        <v>0.476267864231838</v>
       </c>
       <c r="W3">
-        <v>0.1196742305423256</v>
+        <v>0.1573631179415821</v>
       </c>
       <c r="X3">
-        <v>0.06936269180609589</v>
+        <v>0.2310490723999929</v>
       </c>
       <c r="Y3">
-        <v>0.05031153873622969</v>
+        <v>-0.07368595445841086</v>
       </c>
       <c r="Z3">
-        <v>0.1398536097643797</v>
+        <v>0.1226719564215364</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>0.0007695940556697286</v>
       </c>
       <c r="AB3">
-        <v>0.04848518214431398</v>
+        <v>0.07822373316069102</v>
       </c>
       <c r="AC3">
-        <v>-0.04848518214431398</v>
+        <v>-0.07745413910502129</v>
       </c>
       <c r="AD3">
-        <v>6915.3</v>
+        <v>42440.7</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>324.5333806339638</v>
       </c>
       <c r="AF3">
-        <v>6915.3</v>
+        <v>42765.23338063396</v>
       </c>
       <c r="AG3">
-        <v>6061.5</v>
+        <v>38926.13338063396</v>
       </c>
       <c r="AH3">
-        <v>0.4798359677486504</v>
+        <v>0.8414041099836963</v>
       </c>
       <c r="AI3">
-        <v>0.4576759146502886</v>
+        <v>0.8435883494255787</v>
       </c>
       <c r="AJ3">
-        <v>0.4470792152234843</v>
+        <v>0.8284459227270549</v>
       </c>
       <c r="AK3">
-        <v>0.4251953590819176</v>
+        <v>0.8307727332641868</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>442.090625</v>
+      </c>
+      <c r="AP3">
+        <v>405.4805560482704</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Banco del Bajío, S.A., Institución de Banca Múltiple (BMV:BBAJIO O)</t>
+          <t>Grupo Financiero Banorte, S.A.B. de C.V. (BMV:GFNORTE O)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,13 +850,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0984</v>
+        <v>0.0992</v>
       </c>
       <c r="E4">
-        <v>0.145</v>
+        <v>0.136</v>
       </c>
       <c r="F4">
-        <v>0.197</v>
+        <v>0.158</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -865,85 +871,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>195.1</v>
+        <v>2134.4</v>
       </c>
       <c r="L4">
-        <v>0.3461060847968777</v>
+        <v>0.4186739897999215</v>
       </c>
       <c r="M4">
-        <v>110.4</v>
+        <v>1303.9</v>
       </c>
       <c r="N4">
-        <v>0.05168539325842697</v>
+        <v>0.06361946397466738</v>
       </c>
       <c r="O4">
-        <v>0.565863659661712</v>
+        <v>0.610897676161919</v>
       </c>
       <c r="P4">
-        <v>110.4</v>
+        <v>1252</v>
       </c>
       <c r="Q4">
-        <v>0.05168539325842697</v>
+        <v>0.06108717608427298</v>
       </c>
       <c r="R4">
-        <v>0.565863659661712</v>
+        <v>0.5865817091454273</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>51.90000000000009</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.03980366592530109</v>
       </c>
       <c r="U4">
-        <v>529.5</v>
+        <v>4567.2</v>
       </c>
       <c r="V4">
-        <v>0.2478932584269663</v>
+        <v>0.2228413343547057</v>
       </c>
       <c r="W4">
-        <v>0.1264338020867086</v>
+        <v>0.1869214534053789</v>
       </c>
       <c r="X4">
-        <v>0.07179177224322282</v>
+        <v>0.1199957530294871</v>
       </c>
       <c r="Y4">
-        <v>0.05464202984348575</v>
+        <v>0.06692570037589181</v>
       </c>
       <c r="Z4">
-        <v>0.177165539935319</v>
+        <v>0.1510326091786824</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04850844012580475</v>
+        <v>0.07863690032234789</v>
       </c>
       <c r="AC4">
-        <v>-0.04850844012580475</v>
+        <v>-0.07863690032234789</v>
       </c>
       <c r="AD4">
-        <v>2195.2</v>
+        <v>29010.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2195.2</v>
+        <v>29010.5</v>
       </c>
       <c r="AG4">
-        <v>1665.7</v>
+        <v>24443.3</v>
       </c>
       <c r="AH4">
-        <v>0.5068341337273734</v>
+        <v>0.5860020442049214</v>
       </c>
       <c r="AI4">
-        <v>0.5537142136461092</v>
+        <v>0.7049528095566723</v>
       </c>
       <c r="AJ4">
-        <v>0.4381460925375489</v>
+        <v>0.543926602074831</v>
       </c>
       <c r="AK4">
-        <v>0.4849199417758369</v>
+        <v>0.6681198954768596</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -960,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grupo Financiero Banorte, S.A.B. de C.V. (BMV:GFNORTE O)</t>
+          <t>Grupo Elektra, S.A.B. de C.V. (BMV:ELEKTRA *)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,13 +975,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.09210000000000002</v>
-      </c>
-      <c r="E5">
-        <v>0.11</v>
-      </c>
-      <c r="F5">
-        <v>0.133</v>
+        <v>0.0852</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -990,85 +990,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>1558.9</v>
+        <v>-339.3</v>
       </c>
       <c r="L5">
-        <v>0.3769100580270793</v>
+        <v>-0.07977710375961063</v>
       </c>
       <c r="M5">
-        <v>445.5</v>
+        <v>217.7</v>
       </c>
       <c r="N5">
-        <v>0.02381143269462038</v>
+        <v>0.017416</v>
       </c>
       <c r="O5">
-        <v>0.2857784335108089</v>
+        <v>-0.641615089890952</v>
       </c>
       <c r="P5">
-        <v>445.5</v>
+        <v>58.5</v>
       </c>
       <c r="Q5">
-        <v>0.02381143269462038</v>
+        <v>0.00468</v>
       </c>
       <c r="R5">
-        <v>0.2857784335108089</v>
+        <v>-0.1724137931034483</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>159.2</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.7312815801561782</v>
       </c>
       <c r="U5">
-        <v>3306.4</v>
+        <v>1435.4</v>
       </c>
       <c r="V5">
-        <v>0.1767230551324194</v>
+        <v>0.114832</v>
       </c>
       <c r="W5">
-        <v>0.1603311735061195</v>
+        <v>-0.06646294881588999</v>
       </c>
       <c r="X5">
-        <v>0.0797041132716495</v>
+        <v>0.111442379742262</v>
       </c>
       <c r="Y5">
-        <v>0.08062706023447003</v>
+        <v>-0.177905328558152</v>
       </c>
       <c r="Z5">
-        <v>0.1325789752055519</v>
+        <v>0.2546156609195402</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04856987976713101</v>
+        <v>0.07873173132854988</v>
       </c>
       <c r="AC5">
-        <v>-0.04856987976713101</v>
+        <v>-0.07873173132854988</v>
       </c>
       <c r="AD5">
-        <v>25642</v>
+        <v>13948.4</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>25642</v>
+        <v>13948.4</v>
       </c>
       <c r="AG5">
-        <v>22335.6</v>
+        <v>12513</v>
       </c>
       <c r="AH5">
-        <v>0.5781540646877783</v>
+        <v>0.5273816185478138</v>
       </c>
       <c r="AI5">
-        <v>0.6892621653078724</v>
+        <v>0.7479877090717989</v>
       </c>
       <c r="AJ5">
-        <v>0.5441721423507313</v>
+        <v>0.5002598648702674</v>
       </c>
       <c r="AK5">
-        <v>0.6589508403720826</v>
+        <v>0.7269716775599129</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Banco Santander México, S.A., Institución de Banca Múltiple, Grupo Financiero Santander México (BMV:BSMX B)</t>
+          <t>Grupo Financiero Inbursa, S.A.B. de C.V. (BMV:GFINBUR O)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1094,13 +1094,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.06559999999999999</v>
+        <v>0.00191</v>
       </c>
       <c r="E6">
-        <v>0.0354</v>
+        <v>0.0356</v>
       </c>
       <c r="F6">
-        <v>0.08199999999999999</v>
+        <v>0.08349999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1109,103 +1109,97 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.01875827398234381</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.01466782781818553</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>893.6</v>
+        <v>1115.9</v>
       </c>
       <c r="L6">
-        <v>0.2836735341735183</v>
+        <v>0.6816737935247404</v>
       </c>
       <c r="M6">
-        <v>149.488</v>
+        <v>342</v>
       </c>
       <c r="N6">
-        <v>0.01921464286173344</v>
+        <v>0.0331684608670352</v>
       </c>
       <c r="O6">
-        <v>0.1672873769024172</v>
+        <v>0.3064790751859485</v>
       </c>
       <c r="P6">
-        <v>149</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.01915191711975732</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.1667412712623098</v>
+        <v>-0</v>
       </c>
       <c r="S6">
-        <v>0.4879999999999995</v>
+        <v>342</v>
       </c>
       <c r="T6">
-        <v>0.003264476078347423</v>
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>4722.6</v>
+        <v>823.9</v>
       </c>
       <c r="V6">
-        <v>0.6070257972467513</v>
+        <v>0.07990495587236932</v>
       </c>
       <c r="W6">
-        <v>0.1302642895669033</v>
+        <v>0.1362665005922507</v>
       </c>
       <c r="X6">
-        <v>0.1319668700263696</v>
+        <v>0.1011374651581793</v>
       </c>
       <c r="Y6">
-        <v>-0.00170258045946628</v>
+        <v>0.03512903543407137</v>
       </c>
       <c r="Z6">
-        <v>0.07873252594072803</v>
+        <v>0.1156604373476525</v>
       </c>
       <c r="AA6">
-        <v>0.001154835134189425</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05128248037691029</v>
+        <v>0.07888898519476087</v>
       </c>
       <c r="AC6">
-        <v>-0.05012764524272086</v>
+        <v>-0.07888898519476087</v>
       </c>
       <c r="AD6">
-        <v>27788.3</v>
+        <v>7784</v>
       </c>
       <c r="AE6">
-        <v>491.0478056410939</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>28279.34780564109</v>
+        <v>7784</v>
       </c>
       <c r="AG6">
-        <v>23556.74780564109</v>
+        <v>6960.1</v>
       </c>
       <c r="AH6">
-        <v>0.7842467474104406</v>
+        <v>0.430174081237911</v>
       </c>
       <c r="AI6">
-        <v>0.7783903495462878</v>
+        <v>0.4571455418913046</v>
       </c>
       <c r="AJ6">
-        <v>0.751731581238262</v>
+        <v>0.4029911239006201</v>
       </c>
       <c r="AK6">
-        <v>0.7452792554104668</v>
+        <v>0.4295429999691425</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>176.6579783852511</v>
-      </c>
-      <c r="AP6">
-        <v>149.7568201248639</v>
       </c>
     </row>
     <row r="7">
@@ -1216,7 +1210,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Grupo Elektra, S.A.B. de C.V. (BMV:ELEKTRA *)</t>
+          <t>Banco del Bajío, S.A., Institución de Banca Múltiple (BMV:BBAJIO O)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1225,10 +1219,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.104</v>
+        <v>0.109</v>
       </c>
       <c r="E7">
-        <v>0.344</v>
+        <v>0.154</v>
+      </c>
+      <c r="F7">
+        <v>0.15</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1243,216 +1240,91 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>688.6</v>
+        <v>348.2</v>
       </c>
       <c r="L7">
-        <v>0.1967372360789692</v>
+        <v>0.4433409727527375</v>
       </c>
       <c r="M7">
-        <v>116.4</v>
+        <v>233.51</v>
       </c>
       <c r="N7">
-        <v>0.006772206028659696</v>
+        <v>0.06219138679521667</v>
       </c>
       <c r="O7">
-        <v>0.1690386291025269</v>
+        <v>0.6706203331418725</v>
       </c>
       <c r="P7">
-        <v>53.6</v>
+        <v>232.4</v>
       </c>
       <c r="Q7">
-        <v>0.00311847287917663</v>
+        <v>0.06189575731749541</v>
       </c>
       <c r="R7">
-        <v>0.07783909381353471</v>
+        <v>0.6674325100516945</v>
       </c>
       <c r="S7">
-        <v>62.8</v>
+        <v>1.110000000000014</v>
       </c>
       <c r="T7">
-        <v>0.5395189003436426</v>
+        <v>0.004753543745449932</v>
       </c>
       <c r="U7">
-        <v>1271.2</v>
+        <v>547.2</v>
       </c>
       <c r="V7">
-        <v>0.07395900604495022</v>
+        <v>0.1457373425306949</v>
       </c>
       <c r="W7">
-        <v>0.1615559674354222</v>
+        <v>0.196800994743684</v>
       </c>
       <c r="X7">
-        <v>0.06567996413308817</v>
+        <v>0.09984100234256524</v>
       </c>
       <c r="Y7">
-        <v>0.09587600330233402</v>
+        <v>0.09695999240111872</v>
       </c>
       <c r="Z7">
-        <v>0.2575193501868801</v>
+        <v>0.2289715811691719</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.050766436979719</v>
+        <v>0.07891347213699369</v>
       </c>
       <c r="AC7">
-        <v>-0.050766436979719</v>
+        <v>-0.07891347213699369</v>
       </c>
       <c r="AD7">
-        <v>13112.8</v>
+        <v>2664</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>13112.8</v>
+        <v>2664</v>
       </c>
       <c r="AG7">
-        <v>11841.6</v>
+        <v>2116.8</v>
       </c>
       <c r="AH7">
-        <v>0.4327556789117083</v>
+        <v>0.415037312851512</v>
       </c>
       <c r="AI7">
-        <v>0.7197716544077286</v>
+        <v>0.6099599313108185</v>
       </c>
       <c r="AJ7">
-        <v>0.4079160853614426</v>
+        <v>0.360521161543047</v>
       </c>
       <c r="AK7">
-        <v>0.6987513866924728</v>
+        <v>0.554092610527969</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
         <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Banco Actinver S.A., Institución de Banca Múltiple, Grupo Financiero Actinver (BMV:FNOVA 17)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>0.0649</v>
-      </c>
-      <c r="E8">
-        <v>0.204</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>-0.0144760376629669</v>
-      </c>
-      <c r="J8">
-        <v>-0.01023558218593619</v>
-      </c>
-      <c r="K8">
-        <v>6.3</v>
-      </c>
-      <c r="L8">
-        <v>0.04350828729281767</v>
-      </c>
-      <c r="M8">
-        <v>-0</v>
-      </c>
-      <c r="N8">
-        <v>-0</v>
-      </c>
-      <c r="O8">
-        <v>-0</v>
-      </c>
-      <c r="P8">
-        <v>-0</v>
-      </c>
-      <c r="Q8">
-        <v>-0</v>
-      </c>
-      <c r="R8">
-        <v>-0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>42.2</v>
-      </c>
-      <c r="V8">
-        <v>15.17985611510792</v>
-      </c>
-      <c r="W8">
-        <v>0.0371900826446281</v>
-      </c>
-      <c r="X8">
-        <v>6.482160255681829</v>
-      </c>
-      <c r="Y8">
-        <v>-6.444970173037201</v>
-      </c>
-      <c r="Z8">
-        <v>29.6681717355501</v>
-      </c>
-      <c r="AA8">
-        <v>-0.3036710101056921</v>
-      </c>
-      <c r="AB8">
-        <v>0.04893020618565736</v>
-      </c>
-      <c r="AC8">
-        <v>-0.3526012162913494</v>
-      </c>
-      <c r="AD8">
-        <v>754.7</v>
-      </c>
-      <c r="AE8">
-        <v>20.28065126798803</v>
-      </c>
-      <c r="AF8">
-        <v>774.980651267988</v>
-      </c>
-      <c r="AG8">
-        <v>732.780651267988</v>
-      </c>
-      <c r="AH8">
-        <v>0.9964256355789307</v>
-      </c>
-      <c r="AI8">
-        <v>0.7958472477953461</v>
-      </c>
-      <c r="AJ8">
-        <v>0.9962205699894254</v>
-      </c>
-      <c r="AK8">
-        <v>0.7865992603759959</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>385.0510204081633</v>
-      </c>
-      <c r="AP8">
-        <v>373.8676792183612</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/mexico/mexico_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0852</v>
+        <v>0.08355</v>
       </c>
       <c r="E2">
-        <v>0.1053</v>
+        <v>0.1124</v>
       </c>
       <c r="F2">
-        <v>0.11675</v>
+        <v>0.101</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,103 +603,97 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.001989310685289199</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>0.00167681616552411</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>4525.8</v>
+        <v>5699.900000000001</v>
       </c>
       <c r="L2">
-        <v>0.2895548361505291</v>
+        <v>0.3594881303766493</v>
       </c>
       <c r="M2">
-        <v>3080.01</v>
+        <v>663.0450000000001</v>
       </c>
       <c r="N2">
-        <v>0.05587644089997061</v>
+        <v>0.01015118575562258</v>
       </c>
       <c r="O2">
-        <v>0.6805448760440144</v>
+        <v>0.1163257250127195</v>
       </c>
       <c r="P2">
-        <v>2525.8</v>
+        <v>343.6</v>
       </c>
       <c r="Q2">
-        <v>0.04582216110504374</v>
+        <v>0.00526049879816893</v>
       </c>
       <c r="R2">
-        <v>0.5580891776039595</v>
+        <v>0.06028175932911103</v>
       </c>
       <c r="S2">
-        <v>554.21</v>
+        <v>319.445</v>
       </c>
       <c r="T2">
-        <v>0.1799377274749108</v>
+        <v>0.4817847959037471</v>
       </c>
       <c r="U2">
-        <v>11212.8</v>
+        <v>11382</v>
       </c>
       <c r="V2">
-        <v>0.2034186111484022</v>
+        <v>0.1742578501768299</v>
       </c>
       <c r="W2">
-        <v>0.1573631179415821</v>
+        <v>0.2176875340054523</v>
       </c>
       <c r="X2">
-        <v>0.111442379742262</v>
+        <v>0.08680125848186288</v>
       </c>
       <c r="Y2">
-        <v>0.04592073819932005</v>
+        <v>0.1308862755235895</v>
       </c>
       <c r="Z2">
-        <v>0.1571173552032647</v>
+        <v>0.2200170012380431</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07873173132854988</v>
+        <v>0.06716600376466106</v>
       </c>
       <c r="AC2">
-        <v>-0.07873173132854988</v>
+        <v>-0.06716600376466106</v>
       </c>
       <c r="AD2">
-        <v>95847.59999999999</v>
+        <v>63457.60000000001</v>
       </c>
       <c r="AE2">
-        <v>324.5333806339638</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>96172.13338063395</v>
+        <v>63457.60000000001</v>
       </c>
       <c r="AG2">
-        <v>84959.33338063395</v>
+        <v>52075.60000000001</v>
       </c>
       <c r="AH2">
-        <v>0.6356641752361517</v>
+        <v>0.4927804085588307</v>
       </c>
       <c r="AI2">
-        <v>0.7291864486656114</v>
+        <v>0.6475476750261233</v>
       </c>
       <c r="AJ2">
-        <v>0.6065008993736445</v>
+        <v>0.4436020669105208</v>
       </c>
       <c r="AK2">
-        <v>0.7040235561423681</v>
+        <v>0.6012321219930081</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>998.4124999999999</v>
-      </c>
-      <c r="AP2">
-        <v>884.9930560482703</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +704,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Banco Santander México, S.A., Institución de Banca Múltiple, Grupo Financiero Santander México (BMV:BSMX B)</t>
+          <t>Grupo Financiero Banorte, S.A.B. de C.V. (BMV:GFNORTE O)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,13 +713,13 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.07820000000000001</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="E3">
-        <v>0.0746</v>
+        <v>0.125</v>
       </c>
       <c r="F3">
-        <v>0.07539999999999999</v>
+        <v>0.117</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,103 +728,94 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.008062157770427372</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>0.006273594048057571</v>
+        <v>0</v>
       </c>
       <c r="K3">
-        <v>1266.6</v>
+        <v>2926.8</v>
       </c>
       <c r="L3">
-        <v>0.3284154847408406</v>
+        <v>0.446607867671743</v>
       </c>
       <c r="M3">
-        <v>982.9</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.1219357880111155</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.7760145270803727</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>982.9</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.1219357880111155</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.7760145270803727</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>3839.1</v>
+        <v>6272.2</v>
       </c>
       <c r="V3">
-        <v>0.476267864231838</v>
+        <v>0.2153567247044605</v>
       </c>
       <c r="W3">
-        <v>0.1573631179415821</v>
+        <v>0.2438776445492497</v>
       </c>
       <c r="X3">
-        <v>0.2310490723999929</v>
+        <v>0.09456301805057528</v>
       </c>
       <c r="Y3">
-        <v>-0.07368595445841086</v>
+        <v>0.1493146264986744</v>
       </c>
       <c r="Z3">
-        <v>0.1226719564215364</v>
+        <v>0.1866321125477018</v>
       </c>
       <c r="AA3">
-        <v>0.0007695940556697286</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.07822373316069102</v>
+        <v>0.06703453314875693</v>
       </c>
       <c r="AC3">
-        <v>-0.07745413910502129</v>
+        <v>-0.06703453314875693</v>
       </c>
       <c r="AD3">
-        <v>42440.7</v>
+        <v>38207.8</v>
       </c>
       <c r="AE3">
-        <v>324.5333806339638</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>42765.23338063396</v>
+        <v>38207.8</v>
       </c>
       <c r="AG3">
-        <v>38926.13338063396</v>
+        <v>31935.6</v>
       </c>
       <c r="AH3">
-        <v>0.8414041099836963</v>
+        <v>0.5674495971484796</v>
       </c>
       <c r="AI3">
-        <v>0.8435883494255787</v>
+        <v>0.7242937681747352</v>
       </c>
       <c r="AJ3">
-        <v>0.8284459227270549</v>
+        <v>0.5230174106579889</v>
       </c>
       <c r="AK3">
-        <v>0.8307727332641868</v>
+        <v>0.6870885291611804</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>442.090625</v>
-      </c>
-      <c r="AP3">
-        <v>405.4805560482704</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Grupo Financiero Banorte, S.A.B. de C.V. (BMV:GFNORTE O)</t>
+          <t>Grupo Elektra, S.A.B. de C.V. (BMV:ELEKTRA *)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,13 +835,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0992</v>
+        <v>0.07429999999999999</v>
       </c>
       <c r="E4">
-        <v>0.136</v>
-      </c>
-      <c r="F4">
-        <v>0.158</v>
+        <v>-0.0738</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -871,85 +853,85 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>2134.4</v>
+        <v>380.9</v>
       </c>
       <c r="L4">
-        <v>0.4186739897999215</v>
+        <v>0.07544516410164993</v>
       </c>
       <c r="M4">
-        <v>1303.9</v>
+        <v>355.5</v>
       </c>
       <c r="N4">
-        <v>0.06361946397466738</v>
+        <v>0.02318286750224981</v>
       </c>
       <c r="O4">
-        <v>0.610897676161919</v>
+        <v>0.9333158309267525</v>
       </c>
       <c r="P4">
-        <v>1252</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="Q4">
-        <v>0.06108717608427298</v>
+        <v>0.004310513479321273</v>
       </c>
       <c r="R4">
-        <v>0.5865817091454273</v>
+        <v>0.1735363612496718</v>
       </c>
       <c r="S4">
-        <v>51.90000000000009</v>
+        <v>289.4</v>
       </c>
       <c r="T4">
-        <v>0.03980366592530109</v>
+        <v>0.8140646976090014</v>
       </c>
       <c r="U4">
-        <v>4567.2</v>
+        <v>1530.5</v>
       </c>
       <c r="V4">
-        <v>0.2228413343547057</v>
+        <v>0.09980697246749182</v>
       </c>
       <c r="W4">
-        <v>0.1869214534053789</v>
+        <v>0.08105290037026003</v>
       </c>
       <c r="X4">
-        <v>0.1199957530294871</v>
+        <v>0.09021714750301937</v>
       </c>
       <c r="Y4">
-        <v>0.06692570037589181</v>
+        <v>-0.009164247132759346</v>
       </c>
       <c r="Z4">
-        <v>0.1510326091786824</v>
+        <v>0.2966316296614004</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07863690032234789</v>
+        <v>0.06709926586403948</v>
       </c>
       <c r="AC4">
-        <v>-0.07863690032234789</v>
+        <v>-0.06709926586403948</v>
       </c>
       <c r="AD4">
-        <v>29010.5</v>
+        <v>16841.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>29010.5</v>
+        <v>16841.9</v>
       </c>
       <c r="AG4">
-        <v>24443.3</v>
+        <v>15311.4</v>
       </c>
       <c r="AH4">
-        <v>0.5860020442049214</v>
+        <v>0.5234223734713223</v>
       </c>
       <c r="AI4">
-        <v>0.7049528095566723</v>
+        <v>0.7622907784084222</v>
       </c>
       <c r="AJ4">
-        <v>0.543926602074831</v>
+        <v>0.4996214840435946</v>
       </c>
       <c r="AK4">
-        <v>0.6681198954768596</v>
+        <v>0.7445983864457553</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -966,7 +948,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grupo Elektra, S.A.B. de C.V. (BMV:ELEKTRA *)</t>
+          <t>Banco del Bajío, S.A., Institución de Banca Múltiple (BMV:BBAJIO O)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,7 +957,13 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0852</v>
+        <v>0.135</v>
+      </c>
+      <c r="E5">
+        <v>0.179</v>
+      </c>
+      <c r="F5">
+        <v>0.08749999999999999</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -990,85 +978,85 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>-339.3</v>
+        <v>623.3</v>
       </c>
       <c r="L5">
-        <v>-0.07977710375961063</v>
+        <v>0.4821318069306931</v>
       </c>
       <c r="M5">
-        <v>217.7</v>
+        <v>277.845</v>
       </c>
       <c r="N5">
-        <v>0.017416</v>
+        <v>0.06949773631156357</v>
       </c>
       <c r="O5">
-        <v>-0.641615089890952</v>
+        <v>0.4457644793839243</v>
       </c>
       <c r="P5">
-        <v>58.5</v>
+        <v>277.5</v>
       </c>
       <c r="Q5">
-        <v>0.00468</v>
+        <v>0.06941144100652842</v>
       </c>
       <c r="R5">
-        <v>-0.1724137931034483</v>
+        <v>0.4452109738488689</v>
       </c>
       <c r="S5">
-        <v>159.2</v>
+        <v>0.3450000000000273</v>
       </c>
       <c r="T5">
-        <v>0.7312815801561782</v>
+        <v>0.001241699508718988</v>
       </c>
       <c r="U5">
-        <v>1435.4</v>
+        <v>534.5</v>
       </c>
       <c r="V5">
-        <v>0.114832</v>
+        <v>0.1336951899747367</v>
       </c>
       <c r="W5">
-        <v>-0.06646294881588999</v>
+        <v>0.3658937481655415</v>
       </c>
       <c r="X5">
-        <v>0.111442379742262</v>
+        <v>0.08338536946070638</v>
       </c>
       <c r="Y5">
-        <v>-0.177905328558152</v>
+        <v>0.2825083787048351</v>
       </c>
       <c r="Z5">
-        <v>0.2546156609195402</v>
+        <v>0.3388426719505994</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07873173132854988</v>
+        <v>0.06723274166528262</v>
       </c>
       <c r="AC5">
-        <v>-0.07873173132854988</v>
+        <v>-0.06723274166528262</v>
       </c>
       <c r="AD5">
-        <v>13948.4</v>
+        <v>3048.6</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>13948.4</v>
+        <v>3048.6</v>
       </c>
       <c r="AG5">
-        <v>12513</v>
+        <v>2514.1</v>
       </c>
       <c r="AH5">
-        <v>0.5273816185478138</v>
+        <v>0.4326403178883133</v>
       </c>
       <c r="AI5">
-        <v>0.7479877090717989</v>
+        <v>0.5681750410019382</v>
       </c>
       <c r="AJ5">
-        <v>0.5002598648702674</v>
+        <v>0.3860718673218673</v>
       </c>
       <c r="AK5">
-        <v>0.7269716775599129</v>
+        <v>0.5203990809546479</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1094,13 +1082,13 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.00191</v>
+        <v>0.0762</v>
       </c>
       <c r="E6">
-        <v>0.0356</v>
+        <v>0.0998</v>
       </c>
       <c r="F6">
-        <v>0.08349999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1115,19 +1103,19 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>1115.9</v>
+        <v>1768.9</v>
       </c>
       <c r="L6">
-        <v>0.6816737935247404</v>
+        <v>0.5974600601209175</v>
       </c>
       <c r="M6">
-        <v>342</v>
+        <v>29.7</v>
       </c>
       <c r="N6">
-        <v>0.0331684608670352</v>
+        <v>0.001761586732938706</v>
       </c>
       <c r="O6">
-        <v>0.3064790751859485</v>
+        <v>0.01679009553960088</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1139,191 +1127,66 @@
         <v>-0</v>
       </c>
       <c r="S6">
-        <v>342</v>
+        <v>29.7</v>
       </c>
       <c r="T6">
         <v>1</v>
       </c>
       <c r="U6">
-        <v>823.9</v>
+        <v>3044.8</v>
       </c>
       <c r="V6">
-        <v>0.07990495587236932</v>
+        <v>0.1805952621027533</v>
       </c>
       <c r="W6">
-        <v>0.1362665005922507</v>
+        <v>0.191497423461655</v>
       </c>
       <c r="X6">
-        <v>0.1011374651581793</v>
+        <v>0.07433701889789887</v>
       </c>
       <c r="Y6">
-        <v>0.03512903543407137</v>
+        <v>0.1171604045637562</v>
       </c>
       <c r="Z6">
-        <v>0.1156604373476525</v>
+        <v>0.1837129791075894</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.07888898519476087</v>
+        <v>0.06751421062730587</v>
       </c>
       <c r="AC6">
-        <v>-0.07888898519476087</v>
+        <v>-0.06751421062730587</v>
       </c>
       <c r="AD6">
-        <v>7784</v>
+        <v>5359.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>7784</v>
+        <v>5359.3</v>
       </c>
       <c r="AG6">
-        <v>6960.1</v>
+        <v>2314.5</v>
       </c>
       <c r="AH6">
-        <v>0.430174081237911</v>
+        <v>0.2412023889356455</v>
       </c>
       <c r="AI6">
-        <v>0.4571455418913046</v>
+        <v>0.3013280406621087</v>
       </c>
       <c r="AJ6">
-        <v>0.4029911239006201</v>
+        <v>0.1207084482875516</v>
       </c>
       <c r="AK6">
-        <v>0.4295429999691425</v>
+        <v>0.1570131878866819</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Banco del Bajío, S.A., Institución de Banca Múltiple (BMV:BBAJIO O)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.109</v>
-      </c>
-      <c r="E7">
-        <v>0.154</v>
-      </c>
-      <c r="F7">
-        <v>0.15</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>348.2</v>
-      </c>
-      <c r="L7">
-        <v>0.4433409727527375</v>
-      </c>
-      <c r="M7">
-        <v>233.51</v>
-      </c>
-      <c r="N7">
-        <v>0.06219138679521667</v>
-      </c>
-      <c r="O7">
-        <v>0.6706203331418725</v>
-      </c>
-      <c r="P7">
-        <v>232.4</v>
-      </c>
-      <c r="Q7">
-        <v>0.06189575731749541</v>
-      </c>
-      <c r="R7">
-        <v>0.6674325100516945</v>
-      </c>
-      <c r="S7">
-        <v>1.110000000000014</v>
-      </c>
-      <c r="T7">
-        <v>0.004753543745449932</v>
-      </c>
-      <c r="U7">
-        <v>547.2</v>
-      </c>
-      <c r="V7">
-        <v>0.1457373425306949</v>
-      </c>
-      <c r="W7">
-        <v>0.196800994743684</v>
-      </c>
-      <c r="X7">
-        <v>0.09984100234256524</v>
-      </c>
-      <c r="Y7">
-        <v>0.09695999240111872</v>
-      </c>
-      <c r="Z7">
-        <v>0.2289715811691719</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.07891347213699369</v>
-      </c>
-      <c r="AC7">
-        <v>-0.07891347213699369</v>
-      </c>
-      <c r="AD7">
-        <v>2664</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>2664</v>
-      </c>
-      <c r="AG7">
-        <v>2116.8</v>
-      </c>
-      <c r="AH7">
-        <v>0.415037312851512</v>
-      </c>
-      <c r="AI7">
-        <v>0.6099599313108185</v>
-      </c>
-      <c r="AJ7">
-        <v>0.360521161543047</v>
-      </c>
-      <c r="AK7">
-        <v>0.554092610527969</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/mexico/mexico_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08355</v>
+        <v>0.07440000000000001</v>
       </c>
       <c r="E2">
-        <v>0.1124</v>
-      </c>
-      <c r="F2">
-        <v>0.101</v>
+        <v>-0.426</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -609,85 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>5699.900000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L2">
-        <v>0.3594881303766493</v>
+        <v>0.01322069007534372</v>
       </c>
       <c r="M2">
-        <v>663.0450000000001</v>
+        <v>115.4</v>
       </c>
       <c r="N2">
-        <v>0.01015118575562258</v>
+        <v>0.03115214339704136</v>
       </c>
       <c r="O2">
-        <v>0.1163257250127195</v>
+        <v>1.772657450076805</v>
       </c>
       <c r="P2">
-        <v>343.6</v>
+        <v>58.6</v>
       </c>
       <c r="Q2">
-        <v>0.00526049879816893</v>
+        <v>0.01581902602310765</v>
       </c>
       <c r="R2">
-        <v>0.06028175932911103</v>
+        <v>0.9001536098310293</v>
       </c>
       <c r="S2">
-        <v>319.445</v>
+        <v>56.8</v>
       </c>
       <c r="T2">
-        <v>0.4817847959037471</v>
+        <v>0.4922010398613518</v>
       </c>
       <c r="U2">
-        <v>11382</v>
+        <v>1476.8</v>
       </c>
       <c r="V2">
-        <v>0.1742578501768299</v>
+        <v>0.3986610517222762</v>
       </c>
       <c r="W2">
-        <v>0.2176875340054523</v>
+        <v>0.01239598606165622</v>
       </c>
       <c r="X2">
-        <v>0.08680125848186288</v>
+        <v>0.1551002628686178</v>
       </c>
       <c r="Y2">
-        <v>0.1308862755235895</v>
+        <v>-0.1427042768069616</v>
       </c>
       <c r="Z2">
-        <v>0.2200170012380431</v>
+        <v>0.2425545539628589</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.06716600376466106</v>
+        <v>0.07845245776171078</v>
       </c>
       <c r="AC2">
-        <v>-0.06716600376466106</v>
+        <v>-0.07845245776171078</v>
       </c>
       <c r="AD2">
-        <v>63457.60000000001</v>
+        <v>16084.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>63457.60000000001</v>
+        <v>16084.9</v>
       </c>
       <c r="AG2">
-        <v>52075.60000000001</v>
+        <v>14608.1</v>
       </c>
       <c r="AH2">
-        <v>0.4927804085588307</v>
+        <v>0.8128079315589738</v>
       </c>
       <c r="AI2">
-        <v>0.6475476750261233</v>
+        <v>0.7721579753349559</v>
       </c>
       <c r="AJ2">
-        <v>0.4436020669105208</v>
+        <v>0.7977119453924915</v>
       </c>
       <c r="AK2">
-        <v>0.6012321219930081</v>
+        <v>0.7547728411774128</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -704,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Grupo Financiero Banorte, S.A.B. de C.V. (BMV:GFNORTE O)</t>
+          <t>Grupo Elektra, S.A.B. de C.V. (BMV:ELEKTRA *)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,13 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.09089999999999999</v>
+        <v>0.07440000000000001</v>
       </c>
       <c r="E3">
-        <v>0.125</v>
-      </c>
-      <c r="F3">
-        <v>0.117</v>
+        <v>-0.426</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,459 +728,90 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>2926.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L3">
-        <v>0.446607867671743</v>
+        <v>0.01322069007534372</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>115.4</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.03115214339704136</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>1.772657450076805</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>58.6</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01581902602310765</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.9001536098310293</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>56.8</v>
+      </c>
+      <c r="T3">
+        <v>0.4922010398613518</v>
       </c>
       <c r="U3">
-        <v>6272.2</v>
+        <v>1476.8</v>
       </c>
       <c r="V3">
-        <v>0.2153567247044605</v>
+        <v>0.3986610517222762</v>
       </c>
       <c r="W3">
-        <v>0.2438776445492497</v>
+        <v>0.01239598606165622</v>
       </c>
       <c r="X3">
-        <v>0.09456301805057528</v>
+        <v>0.1551002628686178</v>
       </c>
       <c r="Y3">
-        <v>0.1493146264986744</v>
+        <v>-0.1427042768069616</v>
       </c>
       <c r="Z3">
-        <v>0.1866321125477018</v>
+        <v>0.2425545539628589</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.06703453314875693</v>
+        <v>0.07845245776171078</v>
       </c>
       <c r="AC3">
-        <v>-0.06703453314875693</v>
+        <v>-0.07845245776171078</v>
       </c>
       <c r="AD3">
-        <v>38207.8</v>
+        <v>16084.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>38207.8</v>
+        <v>16084.9</v>
       </c>
       <c r="AG3">
-        <v>31935.6</v>
+        <v>14608.1</v>
       </c>
       <c r="AH3">
-        <v>0.5674495971484796</v>
+        <v>0.8128079315589738</v>
       </c>
       <c r="AI3">
-        <v>0.7242937681747352</v>
+        <v>0.7721579753349559</v>
       </c>
       <c r="AJ3">
-        <v>0.5230174106579889</v>
+        <v>0.7977119453924915</v>
       </c>
       <c r="AK3">
-        <v>0.6870885291611804</v>
+        <v>0.7547728411774128</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Grupo Elektra, S.A.B. de C.V. (BMV:ELEKTRA *)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.07429999999999999</v>
-      </c>
-      <c r="E4">
-        <v>-0.0738</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>380.9</v>
-      </c>
-      <c r="L4">
-        <v>0.07544516410164993</v>
-      </c>
-      <c r="M4">
-        <v>355.5</v>
-      </c>
-      <c r="N4">
-        <v>0.02318286750224981</v>
-      </c>
-      <c r="O4">
-        <v>0.9333158309267525</v>
-      </c>
-      <c r="P4">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="Q4">
-        <v>0.004310513479321273</v>
-      </c>
-      <c r="R4">
-        <v>0.1735363612496718</v>
-      </c>
-      <c r="S4">
-        <v>289.4</v>
-      </c>
-      <c r="T4">
-        <v>0.8140646976090014</v>
-      </c>
-      <c r="U4">
-        <v>1530.5</v>
-      </c>
-      <c r="V4">
-        <v>0.09980697246749182</v>
-      </c>
-      <c r="W4">
-        <v>0.08105290037026003</v>
-      </c>
-      <c r="X4">
-        <v>0.09021714750301937</v>
-      </c>
-      <c r="Y4">
-        <v>-0.009164247132759346</v>
-      </c>
-      <c r="Z4">
-        <v>0.2966316296614004</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.06709926586403948</v>
-      </c>
-      <c r="AC4">
-        <v>-0.06709926586403948</v>
-      </c>
-      <c r="AD4">
-        <v>16841.9</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>16841.9</v>
-      </c>
-      <c r="AG4">
-        <v>15311.4</v>
-      </c>
-      <c r="AH4">
-        <v>0.5234223734713223</v>
-      </c>
-      <c r="AI4">
-        <v>0.7622907784084222</v>
-      </c>
-      <c r="AJ4">
-        <v>0.4996214840435946</v>
-      </c>
-      <c r="AK4">
-        <v>0.7445983864457553</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Banco del Bajío, S.A., Institución de Banca Múltiple (BMV:BBAJIO O)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.135</v>
-      </c>
-      <c r="E5">
-        <v>0.179</v>
-      </c>
-      <c r="F5">
-        <v>0.08749999999999999</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>623.3</v>
-      </c>
-      <c r="L5">
-        <v>0.4821318069306931</v>
-      </c>
-      <c r="M5">
-        <v>277.845</v>
-      </c>
-      <c r="N5">
-        <v>0.06949773631156357</v>
-      </c>
-      <c r="O5">
-        <v>0.4457644793839243</v>
-      </c>
-      <c r="P5">
-        <v>277.5</v>
-      </c>
-      <c r="Q5">
-        <v>0.06941144100652842</v>
-      </c>
-      <c r="R5">
-        <v>0.4452109738488689</v>
-      </c>
-      <c r="S5">
-        <v>0.3450000000000273</v>
-      </c>
-      <c r="T5">
-        <v>0.001241699508718988</v>
-      </c>
-      <c r="U5">
-        <v>534.5</v>
-      </c>
-      <c r="V5">
-        <v>0.1336951899747367</v>
-      </c>
-      <c r="W5">
-        <v>0.3658937481655415</v>
-      </c>
-      <c r="X5">
-        <v>0.08338536946070638</v>
-      </c>
-      <c r="Y5">
-        <v>0.2825083787048351</v>
-      </c>
-      <c r="Z5">
-        <v>0.3388426719505994</v>
-      </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0.06723274166528262</v>
-      </c>
-      <c r="AC5">
-        <v>-0.06723274166528262</v>
-      </c>
-      <c r="AD5">
-        <v>3048.6</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>3048.6</v>
-      </c>
-      <c r="AG5">
-        <v>2514.1</v>
-      </c>
-      <c r="AH5">
-        <v>0.4326403178883133</v>
-      </c>
-      <c r="AI5">
-        <v>0.5681750410019382</v>
-      </c>
-      <c r="AJ5">
-        <v>0.3860718673218673</v>
-      </c>
-      <c r="AK5">
-        <v>0.5203990809546479</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Mexico</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Grupo Financiero Inbursa, S.A.B. de C.V. (BMV:GFINBUR O)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.0762</v>
-      </c>
-      <c r="E6">
-        <v>0.0998</v>
-      </c>
-      <c r="F6">
-        <v>0.101</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>1768.9</v>
-      </c>
-      <c r="L6">
-        <v>0.5974600601209175</v>
-      </c>
-      <c r="M6">
-        <v>29.7</v>
-      </c>
-      <c r="N6">
-        <v>0.001761586732938706</v>
-      </c>
-      <c r="O6">
-        <v>0.01679009553960088</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>-0</v>
-      </c>
-      <c r="S6">
-        <v>29.7</v>
-      </c>
-      <c r="T6">
-        <v>1</v>
-      </c>
-      <c r="U6">
-        <v>3044.8</v>
-      </c>
-      <c r="V6">
-        <v>0.1805952621027533</v>
-      </c>
-      <c r="W6">
-        <v>0.191497423461655</v>
-      </c>
-      <c r="X6">
-        <v>0.07433701889789887</v>
-      </c>
-      <c r="Y6">
-        <v>0.1171604045637562</v>
-      </c>
-      <c r="Z6">
-        <v>0.1837129791075894</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.06751421062730587</v>
-      </c>
-      <c r="AC6">
-        <v>-0.06751421062730587</v>
-      </c>
-      <c r="AD6">
-        <v>5359.3</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>5359.3</v>
-      </c>
-      <c r="AG6">
-        <v>2314.5</v>
-      </c>
-      <c r="AH6">
-        <v>0.2412023889356455</v>
-      </c>
-      <c r="AI6">
-        <v>0.3013280406621087</v>
-      </c>
-      <c r="AJ6">
-        <v>0.1207084482875516</v>
-      </c>
-      <c r="AK6">
-        <v>0.1570131878866819</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/mexico/mexico_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.07440000000000001</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="E2">
-        <v>-0.426</v>
+        <v>0.1122</v>
+      </c>
+      <c r="F2">
+        <v>0.1056</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,85 +609,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>65.09999999999999</v>
+        <v>5272.099999999999</v>
       </c>
       <c r="L2">
-        <v>0.01322069007534372</v>
+        <v>0.3392687070452263</v>
       </c>
       <c r="M2">
-        <v>115.4</v>
+        <v>3263.9</v>
       </c>
       <c r="N2">
-        <v>0.03115214339704136</v>
+        <v>0.08776921153189395</v>
       </c>
       <c r="O2">
-        <v>1.772657450076805</v>
+        <v>0.6190891675044101</v>
       </c>
       <c r="P2">
-        <v>58.6</v>
+        <v>2570.8</v>
       </c>
       <c r="Q2">
-        <v>0.01581902602310765</v>
+        <v>0.06913112810018474</v>
       </c>
       <c r="R2">
-        <v>0.9001536098310293</v>
+        <v>0.4876235276265626</v>
       </c>
       <c r="S2">
-        <v>56.8</v>
+        <v>693.1</v>
       </c>
       <c r="T2">
-        <v>0.4922010398613518</v>
+        <v>0.2123533196482735</v>
       </c>
       <c r="U2">
-        <v>1476.8</v>
+        <v>7991.3</v>
       </c>
       <c r="V2">
-        <v>0.3986610517222762</v>
+        <v>0.2148932565687748</v>
       </c>
       <c r="W2">
-        <v>0.01239598606165622</v>
+        <v>0.1717296953596132</v>
       </c>
       <c r="X2">
-        <v>0.1551002628686178</v>
+        <v>0.1013533747618508</v>
       </c>
       <c r="Y2">
-        <v>-0.1427042768069616</v>
+        <v>0.07037632059776242</v>
       </c>
       <c r="Z2">
-        <v>0.2425545539628589</v>
+        <v>0.182535399740497</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07845245776171078</v>
+        <v>0.07102302981162406</v>
       </c>
       <c r="AC2">
-        <v>-0.07845245776171078</v>
+        <v>-0.07102302981162406</v>
       </c>
       <c r="AD2">
-        <v>16084.9</v>
+        <v>57730</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>16084.9</v>
+        <v>57730</v>
       </c>
       <c r="AG2">
-        <v>14608.1</v>
+        <v>49738.7</v>
       </c>
       <c r="AH2">
-        <v>0.8128079315589738</v>
+        <v>0.6082136765373646</v>
       </c>
       <c r="AI2">
-        <v>0.7721579753349559</v>
+        <v>0.6385094294338137</v>
       </c>
       <c r="AJ2">
-        <v>0.7977119453924915</v>
+        <v>0.5721958907576559</v>
       </c>
       <c r="AK2">
-        <v>0.7547728411774128</v>
+        <v>0.6034609523624646</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,117 +704,489 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Grupo Financiero Banorte, S.A.B. de C.V. (BMV:GFNORTE O)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.0706</v>
+      </c>
+      <c r="E3">
+        <v>0.08039999999999999</v>
+      </c>
+      <c r="F3">
+        <v>0.09820000000000001</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>2834.5</v>
+      </c>
+      <c r="L3">
+        <v>0.4385937765949217</v>
+      </c>
+      <c r="M3">
+        <v>2662.9</v>
+      </c>
+      <c r="N3">
+        <v>0.1444935211512166</v>
+      </c>
+      <c r="O3">
+        <v>0.9394602222614218</v>
+      </c>
+      <c r="P3">
+        <v>2092.4</v>
+      </c>
+      <c r="Q3">
+        <v>0.1135372126842185</v>
+      </c>
+      <c r="R3">
+        <v>0.7381901569941789</v>
+      </c>
+      <c r="S3">
+        <v>570.5</v>
+      </c>
+      <c r="T3">
+        <v>0.2142401141612528</v>
+      </c>
+      <c r="U3">
+        <v>5112</v>
+      </c>
+      <c r="V3">
+        <v>0.2773858876131357</v>
+      </c>
+      <c r="W3">
+        <v>0.197370711565109</v>
+      </c>
+      <c r="X3">
+        <v>0.1076723919550396</v>
+      </c>
+      <c r="Y3">
+        <v>0.08969831961006947</v>
+      </c>
+      <c r="Z3">
+        <v>0.1443733552558094</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0.06996602969974633</v>
+      </c>
+      <c r="AC3">
+        <v>-0.06996602969974633</v>
+      </c>
+      <c r="AD3">
+        <v>33887.9</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>33887.9</v>
+      </c>
+      <c r="AG3">
+        <v>28775.9</v>
+      </c>
+      <c r="AH3">
+        <v>0.6477404137461747</v>
+      </c>
+      <c r="AI3">
+        <v>0.7238374949270564</v>
+      </c>
+      <c r="AJ3">
+        <v>0.6095930312614526</v>
+      </c>
+      <c r="AK3">
+        <v>0.6899868121328379</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Banco del Bajío, S.A., Institución de Banca Múltiple (BMV:BBAJIO O)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.115</v>
+      </c>
+      <c r="E4">
+        <v>0.144</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>558.4</v>
+      </c>
+      <c r="L4">
+        <v>0.4580428184726438</v>
+      </c>
+      <c r="M4">
+        <v>419.8</v>
+      </c>
+      <c r="N4">
+        <v>0.1760758325643822</v>
+      </c>
+      <c r="O4">
+        <v>0.7517908309455588</v>
+      </c>
+      <c r="P4">
+        <v>419.8</v>
+      </c>
+      <c r="Q4">
+        <v>0.1760758325643822</v>
+      </c>
+      <c r="R4">
+        <v>0.7517908309455588</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>472.6</v>
+      </c>
+      <c r="V4">
+        <v>0.1982216257025418</v>
+      </c>
+      <c r="W4">
+        <v>0.2410012947777298</v>
+      </c>
+      <c r="X4">
+        <v>0.0950343575686621</v>
+      </c>
+      <c r="Y4">
+        <v>0.1459669372090677</v>
+      </c>
+      <c r="Z4">
+        <v>0.2526433151378751</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.0704484024867566</v>
+      </c>
+      <c r="AC4">
+        <v>-0.0704484024867566</v>
+      </c>
+      <c r="AD4">
+        <v>2792.9</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>2792.9</v>
+      </c>
+      <c r="AG4">
+        <v>2320.3</v>
+      </c>
+      <c r="AH4">
+        <v>0.5394719051206274</v>
+      </c>
+      <c r="AI4">
+        <v>0.5595199935892299</v>
+      </c>
+      <c r="AJ4">
+        <v>0.4932086300350728</v>
+      </c>
+      <c r="AK4">
+        <v>0.5134543040495685</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Grupo Financiero Inbursa, S.A.B. de C.V. (BMV:GFINBUR O)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.143</v>
+      </c>
+      <c r="E5">
+        <v>0.217</v>
+      </c>
+      <c r="F5">
+        <v>0.113</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>1814.1</v>
+      </c>
+      <c r="L5">
+        <v>0.6183658860824215</v>
+      </c>
+      <c r="M5">
+        <v>65.8</v>
+      </c>
+      <c r="N5">
+        <v>0.005193575121354434</v>
+      </c>
+      <c r="O5">
+        <v>0.03627142935891076</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>65.8</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>929.9</v>
+      </c>
+      <c r="V5">
+        <v>0.07339674020284936</v>
+      </c>
+      <c r="W5">
+        <v>0.1460886791541175</v>
+      </c>
+      <c r="X5">
+        <v>0.08027177775496676</v>
+      </c>
+      <c r="Y5">
+        <v>0.06581690139915071</v>
+      </c>
+      <c r="Z5">
+        <v>0.1924772664645908</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0.07159765713649152</v>
+      </c>
+      <c r="AC5">
+        <v>-0.07159765713649152</v>
+      </c>
+      <c r="AD5">
+        <v>4964.3</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>4964.3</v>
+      </c>
+      <c r="AG5">
+        <v>4034.4</v>
+      </c>
+      <c r="AH5">
+        <v>0.2815218500833627</v>
+      </c>
+      <c r="AI5">
+        <v>0.2793012265106335</v>
+      </c>
+      <c r="AJ5">
+        <v>0.2415244344135202</v>
+      </c>
+      <c r="AK5">
+        <v>0.2395141325449267</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>Grupo Elektra, S.A.B. de C.V. (BMV:ELEKTRA *)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="D6">
         <v>0.07440000000000001</v>
       </c>
-      <c r="E3">
+      <c r="E6">
         <v>-0.426</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
         <v>65.09999999999999</v>
       </c>
-      <c r="L3">
+      <c r="L6">
         <v>0.01322069007534372</v>
       </c>
-      <c r="M3">
+      <c r="M6">
         <v>115.4</v>
       </c>
-      <c r="N3">
+      <c r="N6">
         <v>0.03115214339704136</v>
       </c>
-      <c r="O3">
+      <c r="O6">
         <v>1.772657450076805</v>
       </c>
-      <c r="P3">
+      <c r="P6">
         <v>58.6</v>
       </c>
-      <c r="Q3">
+      <c r="Q6">
         <v>0.01581902602310765</v>
       </c>
-      <c r="R3">
+      <c r="R6">
         <v>0.9001536098310293</v>
       </c>
-      <c r="S3">
+      <c r="S6">
         <v>56.8</v>
       </c>
-      <c r="T3">
+      <c r="T6">
         <v>0.4922010398613518</v>
       </c>
-      <c r="U3">
+      <c r="U6">
         <v>1476.8</v>
       </c>
-      <c r="V3">
+      <c r="V6">
         <v>0.3986610517222762</v>
       </c>
-      <c r="W3">
+      <c r="W6">
         <v>0.01239598606165622</v>
       </c>
-      <c r="X3">
-        <v>0.1551002628686178</v>
-      </c>
-      <c r="Y3">
-        <v>-0.1427042768069616</v>
-      </c>
-      <c r="Z3">
+      <c r="X6">
+        <v>0.155075594719182</v>
+      </c>
+      <c r="Y6">
+        <v>-0.1426796086575258</v>
+      </c>
+      <c r="Z6">
         <v>0.2425545539628589</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.07845245776171078</v>
-      </c>
-      <c r="AC3">
-        <v>-0.07845245776171078</v>
-      </c>
-      <c r="AD3">
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0.07844784007979327</v>
+      </c>
+      <c r="AC6">
+        <v>-0.07844784007979327</v>
+      </c>
+      <c r="AD6">
         <v>16084.9</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
         <v>16084.9</v>
       </c>
-      <c r="AG3">
+      <c r="AG6">
         <v>14608.1</v>
       </c>
-      <c r="AH3">
+      <c r="AH6">
         <v>0.8128079315589738</v>
       </c>
-      <c r="AI3">
+      <c r="AI6">
         <v>0.7721579753349559</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ6">
         <v>0.7977119453924915</v>
       </c>
-      <c r="AK3">
+      <c r="AK6">
         <v>0.7547728411774128</v>
       </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
         <v>0</v>
       </c>
     </row>
